--- a/assets/formatos-notas/formato_8_a_10_egb.xlsx
+++ b/assets/formatos-notas/formato_8_a_10_egb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F78D8-0C22-47A8-91A7-EBBDD324C56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC34018E-9502-4877-A929-3174DF88A790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN COMPORTAMENTAL</t>
   </si>
 </sst>
 </file>
@@ -235,7 +238,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,8 +272,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +302,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA9A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9A9A9"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -315,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -332,6 +355,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -674,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE40"/>
+  <dimension ref="A1:AQ40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -683,33 +713,34 @@
     <col min="4" max="4" width="35.88671875" customWidth="1"/>
     <col min="5" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="39.21875" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="33.21875" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="26" max="27" width="0" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="39.21875" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="33.21875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="33.109375" customWidth="1"/>
+    <col min="33" max="33" width="0" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="39.21875" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="38" max="39" width="0" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="39.21875" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="29.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:38" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -723,7 +754,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -736,23 +767,23 @@
       <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V3" t="s">
+      <c r="AH3" t="s">
         <v>53</v>
       </c>
-      <c r="W3" t="s">
+      <c r="AI3" t="s">
         <v>22</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AJ3" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AK3" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AL3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -765,99 +796,99 @@
       <c r="D4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V4" t="s">
+      <c r="AH4" t="s">
         <v>54</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AI4" t="s">
         <v>26</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AJ4" t="s">
         <v>13</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AK4" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AL4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="V5" t="s">
+      <c r="AH5" t="s">
         <v>55</v>
       </c>
-      <c r="W5" t="s">
+      <c r="AI5" t="s">
         <v>27</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AJ5" t="s">
         <v>28</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AK5" t="s">
         <v>29</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AL5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="V6" t="s">
+      <c r="AH6" t="s">
         <v>56</v>
       </c>
-      <c r="W6" t="s">
+      <c r="AI6" t="s">
         <v>31</v>
       </c>
-      <c r="X6" t="s">
+      <c r="AJ6" t="s">
         <v>32</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AK6" t="s">
         <v>33</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AL6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="V7" t="s">
+      <c r="AH7" t="s">
         <v>57</v>
       </c>
-      <c r="W7" t="s">
+      <c r="AI7" t="s">
         <v>35</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AJ7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="V8" t="s">
+      <c r="AH8" t="s">
         <v>58</v>
       </c>
-      <c r="W8" t="s">
+      <c r="AI8" t="s">
         <v>37</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AJ8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -894,17 +925,20 @@
       <c r="L9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V9" t="s">
+      <c r="M9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH9" t="s">
         <v>59</v>
       </c>
-      <c r="W9" t="s">
+      <c r="AI9" t="s">
         <v>39</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AJ9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
@@ -917,14 +951,15 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="W10" t="s">
+      <c r="M10" s="9"/>
+      <c r="AI10" t="s">
         <v>41</v>
       </c>
-      <c r="X10" t="s">
+      <c r="AJ10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
@@ -937,14 +972,15 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-      <c r="W11" t="s">
+      <c r="M11" s="9"/>
+      <c r="AI11" t="s">
         <v>42</v>
       </c>
-      <c r="X11" t="s">
+      <c r="AJ11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -957,14 +993,15 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="W12" t="s">
+      <c r="M12" s="9"/>
+      <c r="AI12" t="s">
         <v>43</v>
       </c>
-      <c r="X12" t="s">
+      <c r="AJ12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
@@ -977,14 +1014,15 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="W13" t="s">
+      <c r="M13" s="9"/>
+      <c r="AI13" t="s">
         <v>44</v>
       </c>
-      <c r="X13" t="s">
+      <c r="AJ13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
@@ -997,14 +1035,15 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="W14" t="s">
+      <c r="M14" s="9"/>
+      <c r="AI14" t="s">
         <v>45</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AJ14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -1017,11 +1056,12 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="W15" t="s">
+      <c r="M15" s="9"/>
+      <c r="AI15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
@@ -1034,11 +1074,12 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="W16" t="s">
+      <c r="M16" s="9"/>
+      <c r="AI16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
@@ -1051,14 +1092,15 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="W17" t="s">
+      <c r="M17" s="10"/>
+      <c r="AI17" t="s">
         <v>42</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AJ17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
@@ -1071,14 +1113,15 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="W18" t="s">
+      <c r="M18" s="10"/>
+      <c r="AI18" t="s">
         <v>43</v>
       </c>
-      <c r="X18" t="s">
+      <c r="AJ18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -1091,14 +1134,15 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="W19" t="s">
+      <c r="M19" s="10"/>
+      <c r="AI19" t="s">
         <v>44</v>
       </c>
-      <c r="X19" t="s">
+      <c r="AJ19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -1111,14 +1155,15 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="W20" t="s">
+      <c r="M20" s="10"/>
+      <c r="AI20" t="s">
         <v>45</v>
       </c>
-      <c r="X20" t="s">
+      <c r="AJ20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -1131,11 +1176,12 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="W21" t="s">
+      <c r="M21" s="10"/>
+      <c r="AI21" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
@@ -1148,11 +1194,12 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="W22" t="s">
+      <c r="M22" s="10"/>
+      <c r="AI22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
@@ -1165,14 +1212,15 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="W23" t="s">
+      <c r="M23" s="10"/>
+      <c r="AI23" t="s">
         <v>42</v>
       </c>
-      <c r="X23" t="s">
+      <c r="AJ23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="4"/>
       <c r="C24" s="3"/>
@@ -1185,14 +1233,15 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="W24" t="s">
+      <c r="M24" s="10"/>
+      <c r="AI24" t="s">
         <v>43</v>
       </c>
-      <c r="X24" t="s">
+      <c r="AJ24" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
@@ -1205,14 +1254,15 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="W25" t="s">
+      <c r="M25" s="10"/>
+      <c r="AI25" t="s">
         <v>44</v>
       </c>
-      <c r="X25" t="s">
+      <c r="AJ25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
@@ -1225,14 +1275,15 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-      <c r="W26" t="s">
+      <c r="M26" s="10"/>
+      <c r="AI26" t="s">
         <v>45</v>
       </c>
-      <c r="X26" t="s">
+      <c r="AJ26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="4"/>
       <c r="C27" s="3"/>
@@ -1245,11 +1296,12 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
-      <c r="W27" t="s">
+      <c r="M27" s="10"/>
+      <c r="AI27" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="B28" s="4"/>
       <c r="C28" s="3"/>
@@ -1262,11 +1314,12 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-      <c r="W28" t="s">
+      <c r="M28" s="10"/>
+      <c r="AI28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
@@ -1279,14 +1332,15 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
-      <c r="W29" t="s">
+      <c r="M29" s="10"/>
+      <c r="AI29" t="s">
         <v>42</v>
       </c>
-      <c r="X29" t="s">
+      <c r="AJ29" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -1299,14 +1353,15 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
-      <c r="W30" t="s">
+      <c r="M30" s="10"/>
+      <c r="AI30" t="s">
         <v>43</v>
       </c>
-      <c r="X30" t="s">
+      <c r="AJ30" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -1319,14 +1374,15 @@
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
-      <c r="W31" t="s">
+      <c r="M31" s="10"/>
+      <c r="AI31" t="s">
         <v>44</v>
       </c>
-      <c r="X31" t="s">
+      <c r="AJ31" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -1339,14 +1395,15 @@
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
-      <c r="W32" t="s">
+      <c r="M32" s="10"/>
+      <c r="AI32" t="s">
         <v>45</v>
       </c>
-      <c r="X32" t="s">
+      <c r="AJ32" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -1359,11 +1416,12 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
-      <c r="W33" t="s">
+      <c r="M33" s="10"/>
+      <c r="AI33" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -1376,11 +1434,12 @@
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
-      <c r="W34" t="s">
+      <c r="M34" s="10"/>
+      <c r="AI34" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -1393,14 +1452,15 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
-      <c r="W35" t="s">
+      <c r="M35" s="10"/>
+      <c r="AI35" t="s">
         <v>42</v>
       </c>
-      <c r="X35" t="s">
+      <c r="AJ35" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -1413,14 +1473,15 @@
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
-      <c r="W36" t="s">
+      <c r="M36" s="10"/>
+      <c r="AI36" t="s">
         <v>43</v>
       </c>
-      <c r="X36" t="s">
+      <c r="AJ36" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -1433,14 +1494,15 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
-      <c r="W37" t="s">
+      <c r="M37" s="10"/>
+      <c r="AI37" t="s">
         <v>44</v>
       </c>
-      <c r="X37" t="s">
+      <c r="AJ37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -1453,14 +1515,15 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
-      <c r="W38" t="s">
+      <c r="M38" s="10"/>
+      <c r="AI38" t="s">
         <v>45</v>
       </c>
-      <c r="X38" t="s">
+      <c r="AJ38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -1473,11 +1536,12 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-      <c r="W39" t="s">
+      <c r="M39" s="10"/>
+      <c r="AI39" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -1490,7 +1554,8 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-      <c r="W40" t="s">
+      <c r="M40" s="10"/>
+      <c r="AI40" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1500,19 +1565,19 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{BA29F8F6-4357-424C-926B-ABF848246A12}">
-      <formula1>$V$4:V$9</formula1>
+      <formula1>$AH$4:AH$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{1111DBC0-3B92-4B3D-A296-AB24C7349FBB}">
-      <formula1>$W$4:$W$18</formula1>
+      <formula1>$AI$4:$AI$18</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{08909813-B489-4B84-A754-485066F9D523}">
-      <formula1>Y$4:Y$6</formula1>
+      <formula1>AK$4:AK$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{D0130D7C-E58C-49AD-B5F3-99115349199D}">
-      <formula1>$X$4:$X$14</formula1>
+      <formula1>$AJ$4:$AJ$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{D03738F8-5189-4E2B-948E-C83D3DB07424}">
-      <formula1>$Z$4:$Z$6</formula1>
+      <formula1>$AL$4:$AL$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/formatos-notas/formato_8_a_10_egb.xlsx
+++ b/assets/formatos-notas/formato_8_a_10_egb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC34018E-9502-4877-A929-3174DF88A790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF566050-939E-4FC6-828B-CAAA548CB580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,10 +225,10 @@
     <t>ANIMACIÓN A LA LECTURA</t>
   </si>
   <si>
-    <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
-  </si>
-  <si>
     <t>EVALUACIÓN COMPORTAMENTAL</t>
+  </si>
+  <si>
+    <t>CÍVICA Y ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
   </si>
 </sst>
 </file>
@@ -923,10 +923,10 @@
         <v>64</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="AH9" t="s">
         <v>59</v>
